--- a/batchstudent/1/AnhDThe187386/Results/AnhDThe187386/TC2/GradeDetail.xlsx
+++ b/batchstudent/1/AnhDThe187386/Results/AnhDThe187386/TC2/GradeDetail.xlsx
@@ -1050,7 +1050,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1109,7 +1109,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>47</x:v>
@@ -1162,7 +1162,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1218,7 +1218,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1277,7 +1277,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>58</x:v>
@@ -1333,7 +1333,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>58</x:v>
@@ -1386,7 +1386,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1445,7 +1445,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>58</x:v>
@@ -1498,7 +1498,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1557,7 +1557,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>58</x:v>
@@ -1610,7 +1610,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P12" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q12" s="0">
         <x:v>4000</x:v>
@@ -1669,7 +1669,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q13" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R13" s="3" t="s">
         <x:v>58</x:v>
@@ -1722,7 +1722,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P14" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q14" s="0">
         <x:v>4000</x:v>
@@ -1778,7 +1778,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1837,7 +1837,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q16" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R16" s="3" t="s">
         <x:v>58</x:v>
@@ -1893,7 +1893,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
         <x:v>58</x:v>
@@ -1946,7 +1946,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P18" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q18" s="0">
         <x:v>4000</x:v>
@@ -2005,7 +2005,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
         <x:v>58</x:v>
@@ -2058,7 +2058,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P20" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q20" s="0">
         <x:v>4000</x:v>
@@ -2117,7 +2117,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>58</x:v>
